--- a/data/trans_dic/P19C07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,44</t>
+          <t>1,65; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,26</t>
+          <t>1,74; 5,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,02</t>
+          <t>0,51; 3,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,99</t>
+          <t>2,5; 5,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,61</t>
+          <t>0,36; 3,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,88</t>
+          <t>2,95; 9,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,88</t>
+          <t>1,6; 6,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,52</t>
+          <t>4,02; 8,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,88</t>
+          <t>1,33; 3,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,54</t>
+          <t>2,66; 6,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,58</t>
+          <t>1,3; 3,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,49</t>
+          <t>3,69; 6,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,26</t>
+          <t>1,63; 5,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,94</t>
+          <t>0,5; 2,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,1</t>
+          <t>1,55; 5,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,2</t>
+          <t>1,62; 5,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,25</t>
+          <t>2,9; 7,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,35</t>
+          <t>0,67; 3,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,54</t>
+          <t>1,6; 5,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,0</t>
+          <t>2,79; 6,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,93</t>
+          <t>2,85; 5,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,62</t>
+          <t>0,84; 2,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,99</t>
+          <t>1,98; 4,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,12</t>
+          <t>2,61; 5,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,34</t>
+          <t>2,58; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,02</t>
+          <t>1,84; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,66</t>
+          <t>1,82; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,42</t>
+          <t>0,63; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,72</t>
+          <t>0,68; 6,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,86</t>
+          <t>1,6; 5,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,66</t>
+          <t>0,77; 8,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,0</t>
+          <t>1,55; 5,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,58</t>
+          <t>2,35; 5,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,49</t>
+          <t>2,02; 4,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,15</t>
+          <t>1,94; 5,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,17</t>
+          <t>0,91; 4,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,22</t>
+          <t>1,98; 4,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,2</t>
+          <t>1,77; 4,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,76</t>
+          <t>1,52; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,95</t>
+          <t>1,83; 4,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,4</t>
+          <t>2,33; 5,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,93</t>
+          <t>2,8; 5,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,03</t>
+          <t>3,02; 5,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,71</t>
+          <t>1,95; 5,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,33</t>
+          <t>2,42; 4,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,4</t>
+          <t>2,47; 4,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,42</t>
+          <t>2,6; 4,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,32</t>
+          <t>2,3; 4,44</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,27</t>
+          <t>1,87; 6,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,04</t>
+          <t>1,19; 4,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,94</t>
+          <t>1,01; 3,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,19</t>
+          <t>1,57; 10,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,07</t>
+          <t>2,72; 6,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,88</t>
+          <t>1,42; 3,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,06</t>
+          <t>1,57; 4,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,97</t>
+          <t>1,85; 4,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,0</t>
+          <t>2,8; 5,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,51</t>
+          <t>1,56; 3,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,5</t>
+          <t>1,59; 3,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,94</t>
+          <t>2,15; 5,01</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,02</t>
+          <t>2,61; 8,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,05</t>
+          <t>7,86; 16,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,35</t>
+          <t>3,77; 10,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 12,49</t>
+          <t>1,35; 13,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,3</t>
+          <t>2,29; 4,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,63</t>
+          <t>3,08; 5,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,55</t>
+          <t>2,85; 5,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,53</t>
+          <t>2,14; 5,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,61</t>
+          <t>2,61; 4,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,34</t>
+          <t>4,48; 7,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,82</t>
+          <t>3,44; 5,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,93</t>
+          <t>2,39; 5,99</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,2</t>
+          <t>2,74; 4,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,09</t>
+          <t>2,71; 4,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,53</t>
+          <t>2,25; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,04</t>
+          <t>2,3; 4,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,22</t>
+          <t>2,82; 4,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,38</t>
+          <t>2,96; 4,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,39</t>
+          <t>2,93; 4,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,59</t>
+          <t>3,01; 4,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,0</t>
+          <t>2,96; 3,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,98</t>
+          <t>2,98; 3,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,8</t>
+          <t>2,82; 3,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,16</t>
+          <t>2,87; 4,08</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6057; 21006</t>
+          <t>6362; 20921</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7172; 24744</t>
+          <t>6864; 22952</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1959; 11688</t>
+          <t>1996; 12714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11713; 29862</t>
+          <t>12468; 28920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>981; 9678</t>
+          <t>966; 8964</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8970; 26091</t>
+          <t>8668; 27272</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4618; 18575</t>
+          <t>5056; 19918</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17912; 37550</t>
+          <t>17704; 38151</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9060; 25375</t>
+          <t>8681; 24884</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19415; 45078</t>
+          <t>18326; 43391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9102; 25197</t>
+          <t>9146; 26431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33477; 60995</t>
+          <t>34618; 59270</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5646; 18807</t>
+          <t>4894; 17668</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1979; 11271</t>
+          <t>1921; 10766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5016; 19302</t>
+          <t>4899; 18721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7598; 23318</t>
+          <t>7258; 23930</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9532; 24169</t>
+          <t>9685; 24118</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2493; 13644</t>
+          <t>2088; 11907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5291; 18467</t>
+          <t>5332; 19249</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10584; 26437</t>
+          <t>10518; 25024</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17385; 37598</t>
+          <t>18039; 37500</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5867; 18254</t>
+          <t>5829; 19066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13070; 32439</t>
+          <t>12888; 30778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21154; 42293</t>
+          <t>21529; 43772</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11354; 27292</t>
+          <t>11107; 26916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9717; 26883</t>
+          <t>9835; 26675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7644; 22927</t>
+          <t>7370; 22959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4322; 29228</t>
+          <t>4145; 28594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>943; 8014</t>
+          <t>952; 9228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3021; 14108</t>
+          <t>3855; 14178</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1115; 12072</t>
+          <t>1080; 11898</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2433; 9900</t>
+          <t>2555; 9879</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13338; 31832</t>
+          <t>13427; 31661</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14668; 34816</t>
+          <t>15641; 36115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10125; 28031</t>
+          <t>10577; 28765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7157; 34394</t>
+          <t>7516; 35103</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16488; 36794</t>
+          <t>17211; 37812</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17286; 40866</t>
+          <t>17238; 40476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14138; 33087</t>
+          <t>13355; 32636</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16868; 39420</t>
+          <t>18242; 40730</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14307; 32226</t>
+          <t>13897; 33589</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19190; 41444</t>
+          <t>19588; 41459</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20648; 41271</t>
+          <t>20656; 40526</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19997; 54792</t>
+          <t>18686; 54542</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35122; 63563</t>
+          <t>35579; 63750</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42211; 73575</t>
+          <t>41267; 72289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39146; 69124</t>
+          <t>40684; 68474</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44946; 84590</t>
+          <t>45055; 86936</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3959; 15539</t>
+          <t>4644; 16439</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4482; 16292</t>
+          <t>4781; 16779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3969; 16763</t>
+          <t>4305; 16689</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7457; 40331</t>
+          <t>6874; 44512</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12434; 32265</t>
+          <t>12393; 30967</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9422; 25990</t>
+          <t>9505; 25763</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8070; 22612</t>
+          <t>8733; 24748</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15330; 32279</t>
+          <t>15073; 32762</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19699; 42253</t>
+          <t>19734; 41613</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16577; 37624</t>
+          <t>16693; 37745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15364; 34417</t>
+          <t>15635; 34716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25577; 61861</t>
+          <t>26875; 62706</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5321; 17014</t>
+          <t>5533; 18073</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16490; 35501</t>
+          <t>17391; 35535</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8523; 25002</t>
+          <t>9110; 24870</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3014; 29130</t>
+          <t>3144; 30768</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19944; 40656</t>
+          <t>21614; 42180</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27820; 52139</t>
+          <t>28457; 53121</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23206; 45771</t>
+          <t>23496; 45330</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15760; 41106</t>
+          <t>15890; 42169</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29267; 53384</t>
+          <t>30263; 56237</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51365; 84111</t>
+          <t>51351; 83227</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36186; 62095</t>
+          <t>36658; 62206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22754; 57906</t>
+          <t>23370; 58484</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>67976; 102751</t>
+          <t>67018; 104667</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79827; 119066</t>
+          <t>78798; 117446</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58757; 93809</t>
+          <t>59678; 95215</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74973; 132312</t>
+          <t>75478; 133840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76587; 115656</t>
+          <t>77366; 114827</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91727; 137779</t>
+          <t>93006; 136126</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85256; 125249</t>
+          <t>83575; 123236</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>108318; 160686</t>
+          <t>105360; 159643</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>156698; 207471</t>
+          <t>153510; 206485</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>180710; 241025</t>
+          <t>180396; 238162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>153324; 209323</t>
+          <t>155413; 206753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>197837; 281759</t>
+          <t>194450; 276606</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,42</t>
+          <t>1,58; 5,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,81</t>
+          <t>1,73; 6,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,28</t>
+          <t>0,51; 3,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,8</t>
+          <t>2,59; 5,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,34</t>
+          <t>0,36; 3,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,28</t>
+          <t>3,05; 9,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,31</t>
+          <t>1,57; 6,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,65</t>
+          <t>4,03; 7,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,8</t>
+          <t>1,38; 3,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,29</t>
+          <t>2,69; 6,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,76</t>
+          <t>1,31; 3,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,31</t>
+          <t>3,5; 6,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,89</t>
+          <t>1,75; 6,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,81</t>
+          <t>0,51; 2,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,91</t>
+          <t>1,77; 6,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,34</t>
+          <t>1,61; 5,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,23</t>
+          <t>2,68; 7,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,8</t>
+          <t>0,66; 3,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,77</t>
+          <t>1,56; 5,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,63</t>
+          <t>2,55; 6,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,92</t>
+          <t>2,75; 5,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,73</t>
+          <t>0,86; 2,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,73</t>
+          <t>2,01; 4,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,3</t>
+          <t>2,43; 4,97</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,26</t>
+          <t>2,49; 6,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,98</t>
+          <t>1,75; 5,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,67</t>
+          <t>1,93; 5,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,33</t>
+          <t>2,21; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,59</t>
+          <t>0,68; 6,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,89</t>
+          <t>1,23; 5,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 8,53</t>
+          <t>0,76; 8,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,99</t>
+          <t>1,47; 5,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,55</t>
+          <t>2,27; 5,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,65</t>
+          <t>2,02; 4,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,28</t>
+          <t>2,06; 5,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,25</t>
+          <t>2,34; 5,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,34</t>
+          <t>1,89; 4,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,16</t>
+          <t>1,78; 4,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,71</t>
+          <t>1,61; 3,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,08</t>
+          <t>2,0; 4,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,63</t>
+          <t>2,34; 5,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,93</t>
+          <t>2,82; 5,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,92</t>
+          <t>3,06; 6,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,69</t>
+          <t>3,9; 7,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,34</t>
+          <t>2,45; 4,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,32</t>
+          <t>2,47; 4,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,38</t>
+          <t>2,48; 4,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,44</t>
+          <t>3,23; 5,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,63</t>
+          <t>1,6; 6,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,16</t>
+          <t>1,02; 3,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,93</t>
+          <t>0,96; 4,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 10,14</t>
+          <t>1,35; 6,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,79</t>
+          <t>2,77; 6,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,85</t>
+          <t>1,45; 4,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,44</t>
+          <t>1,55; 4,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,02</t>
+          <t>2,21; 4,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,91</t>
+          <t>2,72; 5,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,52</t>
+          <t>1,53; 3,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,53</t>
+          <t>1,51; 3,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,01</t>
+          <t>2,07; 4,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,52</t>
+          <t>2,55; 8,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 16,06</t>
+          <t>8,2; 16,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,3</t>
+          <t>3,75; 10,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,19</t>
+          <t>1,65; 11,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,46</t>
+          <t>2,25; 4,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,74</t>
+          <t>3,12; 5,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,49</t>
+          <t>2,87; 5,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,67</t>
+          <t>2,28; 5,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,86</t>
+          <t>2,51; 4,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,26</t>
+          <t>4,43; 7,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,83</t>
+          <t>3,39; 5,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,99</t>
+          <t>2,43; 5,44</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,27</t>
+          <t>2,76; 4,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,03</t>
+          <t>2,62; 4,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,59</t>
+          <t>2,26; 3,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,08</t>
+          <t>2,77; 4,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,19</t>
+          <t>2,77; 4,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,33</t>
+          <t>2,98; 4,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,32</t>
+          <t>2,98; 4,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,56</t>
+          <t>3,57; 4,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,98</t>
+          <t>3,0; 3,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,93</t>
+          <t>2,97; 3,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,75</t>
+          <t>2,82; 3,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,08</t>
+          <t>3,31; 4,31</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>48498</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6362; 20921</t>
+          <t>6096; 20541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6864; 22952</t>
+          <t>6828; 24030</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1996; 12714</t>
+          <t>1963; 12004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12468; 28920</t>
+          <t>13994; 31496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>966; 8964</t>
+          <t>965; 8773</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8668; 27272</t>
+          <t>8968; 27300</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5056; 19918</t>
+          <t>4952; 19329</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17704; 38151</t>
+          <t>19399; 38196</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8681; 24884</t>
+          <t>9044; 24700</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18326; 43391</t>
+          <t>18555; 42158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9146; 26431</t>
+          <t>9186; 26748</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34618; 59270</t>
+          <t>35838; 63827</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31525</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4894; 17668</t>
+          <t>5241; 18998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1921; 10766</t>
+          <t>1942; 11011</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4899; 18721</t>
+          <t>5605; 19385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7258; 23930</t>
+          <t>7721; 25155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9685; 24118</t>
+          <t>8937; 24033</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2088; 11907</t>
+          <t>2075; 11975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5332; 19249</t>
+          <t>5217; 17364</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10518; 25024</t>
+          <t>10664; 27290</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18039; 37500</t>
+          <t>17448; 37136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5829; 19066</t>
+          <t>5980; 19165</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12888; 30778</t>
+          <t>13080; 31750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21529; 43772</t>
+          <t>21781; 44591</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>23842</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11107; 26916</t>
+          <t>10727; 27140</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9835; 26675</t>
+          <t>9387; 27379</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7370; 22959</t>
+          <t>7806; 22579</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4145; 28594</t>
+          <t>10264; 30978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>952; 9228</t>
+          <t>956; 8601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3855; 14178</t>
+          <t>2969; 13523</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1080; 11898</t>
+          <t>1066; 11386</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2555; 9879</t>
+          <t>2723; 10797</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13427; 31661</t>
+          <t>12954; 30418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15641; 36115</t>
+          <t>15698; 34773</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10577; 28765</t>
+          <t>11235; 28833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7516; 35103</t>
+          <t>15194; 36304</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64992</t>
+          <t>78223</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17211; 37812</t>
+          <t>16491; 36774</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17238; 40476</t>
+          <t>17358; 40908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13355; 32636</t>
+          <t>14175; 33120</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18242; 40730</t>
+          <t>21871; 51171</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13897; 33589</t>
+          <t>13966; 33601</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19588; 41459</t>
+          <t>19737; 41712</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20656; 40526</t>
+          <t>20941; 42078</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18686; 54542</t>
+          <t>32645; 58535</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35579; 63750</t>
+          <t>35927; 63485</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41267; 72289</t>
+          <t>41261; 72000</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40684; 68474</t>
+          <t>38821; 64961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45055; 86936</t>
+          <t>62333; 99549</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39007</t>
+          <t>39122</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4644; 16439</t>
+          <t>3970; 15901</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4781; 16779</t>
+          <t>4103; 16108</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4305; 16689</t>
+          <t>4067; 17234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6874; 44512</t>
+          <t>6887; 34125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12393; 30967</t>
+          <t>12638; 30780</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9505; 25763</t>
+          <t>9680; 26814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8733; 24748</t>
+          <t>8624; 24610</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15073; 32762</t>
+          <t>17514; 33891</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19734; 41613</t>
+          <t>19158; 41367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16693; 37745</t>
+          <t>16437; 37096</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15635; 34716</t>
+          <t>14798; 35369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26875; 62706</t>
+          <t>27042; 57684</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>39311</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5533; 18073</t>
+          <t>5416; 17383</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17391; 35535</t>
+          <t>18145; 37297</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9110; 24870</t>
+          <t>9064; 24679</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3144; 30768</t>
+          <t>3718; 26607</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21614; 42180</t>
+          <t>21320; 42911</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28457; 53121</t>
+          <t>28899; 53640</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23496; 45330</t>
+          <t>23668; 44541</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15890; 42169</t>
+          <t>18662; 44906</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30263; 56237</t>
+          <t>29032; 52738</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51351; 83227</t>
+          <t>50757; 82615</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36658; 62206</t>
+          <t>36188; 63252</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23370; 58484</t>
+          <t>25420; 56791</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103043</t>
+          <t>112849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>134170</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>237213</t>
+          <t>260520</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>67018; 104667</t>
+          <t>67657; 104336</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>78798; 117446</t>
+          <t>76165; 118646</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59678; 95215</t>
+          <t>59910; 94019</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75478; 133840</t>
+          <t>91723; 140413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77366; 114827</t>
+          <t>75897; 114746</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93006; 136126</t>
+          <t>93676; 137436</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83575; 123236</t>
+          <t>85092; 124134</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>105360; 159643</t>
+          <t>126126; 175476</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>153510; 206485</t>
+          <t>155812; 204843</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>180396; 238162</t>
+          <t>179516; 236834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155413; 206753</t>
+          <t>155312; 206020</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>194450; 276606</t>
+          <t>226719; 295335</t>
         </is>
       </c>
     </row>
